--- a/Honda_Logi/Excel_Format/見積書(部単外装).xlsx
+++ b/Honda_Logi/Excel_Format/見積書(部単外装).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\01_hida_data\78_Honda_ロジ\01_PG\git\Honda_Logi\Excel_Format\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFCB3A55-78FC-4630-AC8E-E162E406DFFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BD21866-E6F1-4774-8DC2-655D4EDA8511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{13F1AECC-0018-455B-A1D0-9EDBF251BF86}"/>
+    <workbookView xWindow="29400" yWindow="7215" windowWidth="23040" windowHeight="12735" xr2:uid="{13F1AECC-0018-455B-A1D0-9EDBF251BF86}"/>
   </bookViews>
   <sheets>
     <sheet name="見積書(部単外装)" sheetId="1" r:id="rId1"/>

--- a/Honda_Logi/Excel_Format/見積書(部単外装).xlsx
+++ b/Honda_Logi/Excel_Format/見積書(部単外装).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\01_hida_data\78_Honda_ロジ\01_PG\git\Honda_Logi\Excel_Format\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BD21866-E6F1-4774-8DC2-655D4EDA8511}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E109C396-208D-4CA0-923D-6D5C11EA7D84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29400" yWindow="7215" windowWidth="23040" windowHeight="12735" xr2:uid="{13F1AECC-0018-455B-A1D0-9EDBF251BF86}"/>
+    <workbookView xWindow="28680" yWindow="1965" windowWidth="25440" windowHeight="15390" xr2:uid="{13F1AECC-0018-455B-A1D0-9EDBF251BF86}"/>
   </bookViews>
   <sheets>
     <sheet name="見積書(部単外装)" sheetId="1" r:id="rId1"/>
@@ -119,7 +119,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -156,6 +156,14 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -268,12 +276,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="38" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -310,8 +321,18 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="40" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="桁区切り" xfId="1" builtinId="6"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -683,20 +704,41 @@
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="B2:J4"/>
+  <dimension ref="B1:J4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="8" width="11.125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="16.125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.125" style="1" customWidth="1"/>
+    <col min="2" max="4" width="11.125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="11.125" style="13" customWidth="1"/>
+    <col min="6" max="8" width="11.125" style="14" customWidth="1"/>
+    <col min="9" max="9" width="16.125" style="14" customWidth="1"/>
+    <col min="10" max="10" width="11.125" style="14" customWidth="1"/>
     <col min="11" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+    </row>
     <row r="2" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B3" s="2"/>
